--- a/downloads/telangana-hyderabad.xlsx
+++ b/downloads/telangana-hyderabad.xlsx
@@ -46405,7 +46405,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Electors on the roll before the revision in the constituency, counted from the lists behind the part explorer.</t>
+          <t>Electors on the roll the revision started from, counted from the lists behind the part explorer. In Charminar, Yakutpura and Bahadurpura it equals the Chief Electoral Officer's pre-revision total exactly, and in Chandrayangutta to within one. Malakpet's export is a different count. The Commission's order of 14 May 2026 does not give the date of that roll.</t>
         </is>
       </c>
     </row>
@@ -46660,7 +46660,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Electors on the roll before the revision in the part, as a count (parts with fewer than 100 electors are left out of the file).</t>
+          <t>Electors in the part on the roll the revision started from, counted from the lists (parts with fewer than 100 electors are left out of the file). The Commission's order of 14 May 2026 does not give the date of that roll.</t>
         </is>
       </c>
     </row>

--- a/downloads/telangana-hyderabad.xlsx
+++ b/downloads/telangana-hyderabad.xlsx
@@ -741,13 +741,13 @@
         <v>94174</v>
       </c>
       <c r="D2" t="n">
-        <v>39.66</v>
+        <v>39.655</v>
       </c>
       <c r="E2" t="n">
         <v>50168</v>
       </c>
       <c r="F2" t="n">
-        <v>21.12</v>
+        <v>21.1249</v>
       </c>
       <c r="G2" t="n">
         <v>42238</v>
@@ -762,10 +762,10 @@
         <v>5619</v>
       </c>
       <c r="K2" t="n">
-        <v>38.14</v>
+        <v>38.1442</v>
       </c>
       <c r="L2" t="n">
-        <v>41.11</v>
+        <v>41.113</v>
       </c>
       <c r="M2" t="n">
         <v>22853</v>
@@ -784,13 +784,13 @@
         <v>154982</v>
       </c>
       <c r="D3" t="n">
-        <v>41.33</v>
+        <v>41.3343</v>
       </c>
       <c r="E3" t="n">
         <v>87367</v>
       </c>
       <c r="F3" t="n">
-        <v>23.3</v>
+        <v>23.3011</v>
       </c>
       <c r="G3" t="n">
         <v>103548</v>
@@ -805,10 +805,10 @@
         <v>11860</v>
       </c>
       <c r="K3" t="n">
-        <v>40.31</v>
+        <v>40.3108</v>
       </c>
       <c r="L3" t="n">
-        <v>42.42</v>
+        <v>42.4157</v>
       </c>
       <c r="M3" t="n">
         <v>878</v>
@@ -827,13 +827,13 @@
         <v>142688</v>
       </c>
       <c r="D4" t="n">
-        <v>45.09</v>
+        <v>45.0896</v>
       </c>
       <c r="E4" t="n">
         <v>68188</v>
       </c>
       <c r="F4" t="n">
-        <v>21.55</v>
+        <v>21.5475</v>
       </c>
       <c r="G4" t="n">
         <v>116132</v>
@@ -848,10 +848,10 @@
         <v>6973</v>
       </c>
       <c r="K4" t="n">
-        <v>45.08</v>
+        <v>45.0789</v>
       </c>
       <c r="L4" t="n">
-        <v>47.43</v>
+        <v>47.4301</v>
       </c>
       <c r="M4" t="n">
         <v>26106</v>
@@ -870,13 +870,13 @@
         <v>148869</v>
       </c>
       <c r="D5" t="n">
-        <v>39.46</v>
+        <v>39.4565</v>
       </c>
       <c r="E5" t="n">
         <v>80246</v>
       </c>
       <c r="F5" t="n">
-        <v>21.27</v>
+        <v>21.2685</v>
       </c>
       <c r="G5" t="n">
         <v>91410</v>
@@ -891,10 +891,10 @@
         <v>6313</v>
       </c>
       <c r="K5" t="n">
-        <v>40.01</v>
+        <v>40.0076</v>
       </c>
       <c r="L5" t="n">
-        <v>38.97</v>
+        <v>38.9719</v>
       </c>
       <c r="M5" t="n">
         <v>81660</v>
@@ -913,13 +913,13 @@
         <v>121350</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57</v>
+        <v>34.5704</v>
       </c>
       <c r="E6" t="n">
         <v>84003</v>
       </c>
       <c r="F6" t="n">
-        <v>23.93</v>
+        <v>23.9309</v>
       </c>
       <c r="G6" t="n">
         <v>71853</v>
@@ -934,10 +934,10 @@
         <v>9200</v>
       </c>
       <c r="K6" t="n">
-        <v>35.79</v>
+        <v>35.7895</v>
       </c>
       <c r="L6" t="n">
-        <v>33.41</v>
+        <v>33.413</v>
       </c>
       <c r="M6" t="n">
         <v>67025</v>

--- a/downloads/telangana-hyderabad.xlsx
+++ b/downloads/telangana-hyderabad.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>The five Old City constituencies, with names struck off and summoned to hearings</t>
+          <t>The five Old City constituencies, with names left off the draft and summoned to hearings</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -46372,7 +46372,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Names on the September 2026 list of absent, shifted and dead electors, struck off the draft roll, as a count.</t>
+          <t>Names on the September 2026 list of absent, shifted and dead electors, left off the draft roll, as a count.</t>
         </is>
       </c>
     </row>
@@ -46389,7 +46389,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Names struck off per 100 electors on the roll before the revision.</t>
+          <t>Names left off the draft per 100 electors on the roll before the revision.</t>
         </is>
       </c>
     </row>
@@ -46440,7 +46440,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Names struck off with the reason permanently shifted, as a count, where the reason is what the officer wrote down, and nobody checked it.</t>
+          <t>Names left off with the reason permanently shifted, as a count, where the reason is what the officer wrote down, and nobody checked it.</t>
         </is>
       </c>
     </row>
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Names struck off with the reason untraceable or absent, as a count.</t>
+          <t>Names left off with the reason untraceable or absent, as a count.</t>
         </is>
       </c>
     </row>
@@ -46474,7 +46474,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Names struck off with the reason death, as a count.</t>
+          <t>Names left off with the reason death, as a count.</t>
         </is>
       </c>
     </row>
@@ -46491,7 +46491,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Names struck off with the reason already enrolled somewhere else, as a count.</t>
+          <t>Names left off with the reason already enrolled somewhere else, as a count.</t>
         </is>
       </c>
     </row>
@@ -46508,7 +46508,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Women struck off per 100 women on the roll before the revision.</t>
+          <t>Women left off the draft per 100 women on the roll before the revision.</t>
         </is>
       </c>
     </row>
@@ -46525,7 +46525,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Men struck off per 100 men on the roll before the revision.</t>
+          <t>Men left off the draft per 100 men on the roll before the revision.</t>
         </is>
       </c>
     </row>
@@ -46627,7 +46627,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Names in the part on the September 2026 list of absent, shifted and dead electors, struck off the draft roll, as a count.</t>
+          <t>Names in the part on the September 2026 list of absent, shifted and dead electors, left off the draft roll, as a count.</t>
         </is>
       </c>
     </row>
@@ -46644,7 +46644,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Names struck off per 100 electors in the part.</t>
+          <t>Names left off the draft per 100 electors in the part.</t>
         </is>
       </c>
     </row>
@@ -46678,7 +46678,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Names struck off per 100 electors whose names were guessed to be Muslim, left blank where the part has fewer than 20 such electors.</t>
+          <t>Names left off the draft per 100 electors whose names were guessed to be Muslim, left blank where the part has fewer than 20 such electors.</t>
         </is>
       </c>
     </row>
@@ -46695,7 +46695,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Names struck off per 100 electors whose names were guessed to be Hindu, left blank where the part has fewer than 20 such electors.</t>
+          <t>Names left off the draft per 100 electors whose names were guessed to be Hindu, left blank where the part has fewer than 20 such electors.</t>
         </is>
       </c>
     </row>
@@ -46712,7 +46712,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The share of the part's struck-off names entered as untraceable or absent, as a percentage, where the reason is what the officer wrote down, and nobody checked it.</t>
+          <t>The share of the part's names left off entered as untraceable or absent, as a percentage, where the reason is what the officer wrote down, and nobody checked it.</t>
         </is>
       </c>
     </row>
